--- a/irrigation.xlsx
+++ b/irrigation.xlsx
@@ -1,20 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ugent\Papers\4th_pedotransfer\github\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ugent\Papers\4th_pedotransfer\github\upload\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C68F46E-E6F2-469C-AF99-C344463C12AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40AA0552-923F-420E-8841-D853EE87898E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="1" xr2:uid="{B307A562-199E-4677-9568-3B9D55243B60}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{B307A562-199E-4677-9568-3B9D55243B60}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="final" sheetId="2" r:id="rId2"/>
+    <sheet name="final" sheetId="2" r:id="rId1"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -26,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="8">
   <si>
     <t>rainwater</t>
   </si>
@@ -35,12 +34,6 @@
   </si>
   <si>
     <t>potato</t>
-  </si>
-  <si>
-    <t>-</t>
-  </si>
-  <si>
-    <t>TOTAAL</t>
   </si>
   <si>
     <t>cauliflower</t>
@@ -94,9 +87,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -411,551 +403,6 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{76319BA8-C3BF-4BF7-A57F-076C09EC3DDF}">
-  <dimension ref="A2:P19"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="2" max="2" width="12.1796875" style="2" customWidth="1"/>
-    <col min="3" max="3" width="15.7265625" customWidth="1"/>
-    <col min="7" max="7" width="16.08984375" customWidth="1"/>
-    <col min="8" max="8" width="12.1796875" style="2" customWidth="1"/>
-    <col min="14" max="14" width="14.90625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B2" s="2">
-        <v>43584</v>
-      </c>
-      <c r="C2">
-        <v>5.5</v>
-      </c>
-      <c r="G2" t="s">
-        <v>5</v>
-      </c>
-      <c r="H2" s="2">
-        <v>43592</v>
-      </c>
-      <c r="I2">
-        <v>25</v>
-      </c>
-      <c r="J2" t="s">
-        <v>3</v>
-      </c>
-      <c r="M2" t="s">
-        <v>2</v>
-      </c>
-      <c r="N2" s="2">
-        <v>43938</v>
-      </c>
-      <c r="O2">
-        <v>10</v>
-      </c>
-      <c r="P2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B3" s="2">
-        <v>43585</v>
-      </c>
-      <c r="C3">
-        <v>2.5</v>
-      </c>
-      <c r="G3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H3" s="2">
-        <v>43658</v>
-      </c>
-      <c r="I3">
-        <v>17</v>
-      </c>
-      <c r="J3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M3" t="s">
-        <v>2</v>
-      </c>
-      <c r="N3" s="2">
-        <v>43941</v>
-      </c>
-      <c r="O3">
-        <v>10</v>
-      </c>
-      <c r="P3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" s="2">
-        <v>43588</v>
-      </c>
-      <c r="C4">
-        <v>6</v>
-      </c>
-      <c r="G4" t="s">
-        <v>5</v>
-      </c>
-      <c r="H4" s="2">
-        <v>43663</v>
-      </c>
-      <c r="I4">
-        <v>10</v>
-      </c>
-      <c r="J4" t="s">
-        <v>3</v>
-      </c>
-      <c r="M4" t="s">
-        <v>2</v>
-      </c>
-      <c r="N4" s="2">
-        <v>43957</v>
-      </c>
-      <c r="O4">
-        <v>10</v>
-      </c>
-      <c r="P4" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5" s="2">
-        <v>43591</v>
-      </c>
-      <c r="C5">
-        <v>6</v>
-      </c>
-      <c r="G5" t="s">
-        <v>5</v>
-      </c>
-      <c r="H5" s="2">
-        <v>43670</v>
-      </c>
-      <c r="I5">
-        <v>15</v>
-      </c>
-      <c r="J5" t="s">
-        <v>3</v>
-      </c>
-      <c r="M5" t="s">
-        <v>2</v>
-      </c>
-      <c r="N5" s="2">
-        <v>43971</v>
-      </c>
-      <c r="O5">
-        <v>15</v>
-      </c>
-      <c r="P5" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6" s="2">
-        <v>43595</v>
-      </c>
-      <c r="C6">
-        <v>7</v>
-      </c>
-      <c r="G6" t="s">
-        <v>5</v>
-      </c>
-      <c r="H6" s="2">
-        <v>43675</v>
-      </c>
-      <c r="I6">
-        <v>10</v>
-      </c>
-      <c r="J6" t="s">
-        <v>3</v>
-      </c>
-      <c r="M6" t="s">
-        <v>2</v>
-      </c>
-      <c r="N6" s="2">
-        <v>43976</v>
-      </c>
-      <c r="O6" t="s">
-        <v>3</v>
-      </c>
-      <c r="P6">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B7" s="2">
-        <v>43606</v>
-      </c>
-      <c r="C7">
-        <v>8</v>
-      </c>
-      <c r="G7" t="s">
-        <v>5</v>
-      </c>
-      <c r="H7" s="2">
-        <v>43680</v>
-      </c>
-      <c r="I7">
-        <v>20</v>
-      </c>
-      <c r="J7" t="s">
-        <v>3</v>
-      </c>
-      <c r="M7" t="s">
-        <v>2</v>
-      </c>
-      <c r="N7" s="2">
-        <v>43977</v>
-      </c>
-      <c r="O7" t="s">
-        <v>3</v>
-      </c>
-      <c r="P7">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
-        <v>6</v>
-      </c>
-      <c r="B8" s="2">
-        <v>43612</v>
-      </c>
-      <c r="D8">
-        <v>10</v>
-      </c>
-      <c r="G8" t="s">
-        <v>5</v>
-      </c>
-      <c r="H8" s="2">
-        <v>43685</v>
-      </c>
-      <c r="I8">
-        <v>15</v>
-      </c>
-      <c r="J8" t="s">
-        <v>3</v>
-      </c>
-      <c r="M8" t="s">
-        <v>2</v>
-      </c>
-      <c r="N8" s="2">
-        <v>43986</v>
-      </c>
-      <c r="O8">
-        <v>20</v>
-      </c>
-      <c r="P8" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A9" t="s">
-        <v>6</v>
-      </c>
-      <c r="B9" s="2">
-        <v>43616</v>
-      </c>
-      <c r="D9">
-        <v>20</v>
-      </c>
-      <c r="G9" t="s">
-        <v>5</v>
-      </c>
-      <c r="H9" s="2">
-        <v>43693</v>
-      </c>
-      <c r="I9">
-        <v>10</v>
-      </c>
-      <c r="J9" t="s">
-        <v>3</v>
-      </c>
-      <c r="M9" t="s">
-        <v>2</v>
-      </c>
-      <c r="N9" s="2">
-        <v>43993</v>
-      </c>
-      <c r="O9" t="s">
-        <v>3</v>
-      </c>
-      <c r="P9">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A10" t="s">
-        <v>6</v>
-      </c>
-      <c r="B10" s="2">
-        <v>43621</v>
-      </c>
-      <c r="D10">
-        <v>20</v>
-      </c>
-      <c r="G10" t="s">
-        <v>5</v>
-      </c>
-      <c r="H10" s="2">
-        <v>43701</v>
-      </c>
-      <c r="I10" t="s">
-        <v>3</v>
-      </c>
-      <c r="J10">
-        <v>15</v>
-      </c>
-      <c r="M10" t="s">
-        <v>2</v>
-      </c>
-      <c r="N10" s="2">
-        <v>43994</v>
-      </c>
-      <c r="O10" t="s">
-        <v>3</v>
-      </c>
-      <c r="P10">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="B11" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C11">
-        <v>35</v>
-      </c>
-      <c r="D11">
-        <v>50</v>
-      </c>
-      <c r="G11" t="s">
-        <v>5</v>
-      </c>
-      <c r="H11" s="2">
-        <v>43707</v>
-      </c>
-      <c r="I11">
-        <v>20</v>
-      </c>
-      <c r="J11" t="s">
-        <v>3</v>
-      </c>
-      <c r="M11" t="s">
-        <v>2</v>
-      </c>
-      <c r="N11" s="2">
-        <v>43999</v>
-      </c>
-      <c r="O11">
-        <v>15</v>
-      </c>
-      <c r="P11" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="G12" t="s">
-        <v>5</v>
-      </c>
-      <c r="H12" s="2">
-        <v>43714</v>
-      </c>
-      <c r="I12" t="s">
-        <v>3</v>
-      </c>
-      <c r="J12">
-        <v>25</v>
-      </c>
-      <c r="M12" t="s">
-        <v>2</v>
-      </c>
-      <c r="N12" s="2">
-        <v>44005</v>
-      </c>
-      <c r="O12" t="s">
-        <v>3</v>
-      </c>
-      <c r="P12">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="G13" t="s">
-        <v>5</v>
-      </c>
-      <c r="H13" s="2">
-        <v>43721</v>
-      </c>
-      <c r="I13">
-        <v>13</v>
-      </c>
-      <c r="J13" t="s">
-        <v>3</v>
-      </c>
-      <c r="M13" t="s">
-        <v>2</v>
-      </c>
-      <c r="N13" s="2">
-        <v>44006</v>
-      </c>
-      <c r="O13" t="s">
-        <v>3</v>
-      </c>
-      <c r="P13">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="G14" t="s">
-        <v>5</v>
-      </c>
-      <c r="H14" s="2">
-        <v>43728</v>
-      </c>
-      <c r="I14" t="s">
-        <v>3</v>
-      </c>
-      <c r="J14">
-        <v>25</v>
-      </c>
-      <c r="M14" t="s">
-        <v>2</v>
-      </c>
-      <c r="N14" s="2">
-        <v>44014</v>
-      </c>
-      <c r="O14" t="s">
-        <v>3</v>
-      </c>
-      <c r="P14">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="G15" t="s">
-        <v>5</v>
-      </c>
-      <c r="H15" s="2">
-        <v>43735</v>
-      </c>
-      <c r="I15" t="s">
-        <v>3</v>
-      </c>
-      <c r="J15">
-        <v>10</v>
-      </c>
-      <c r="M15" t="s">
-        <v>2</v>
-      </c>
-      <c r="N15" s="2">
-        <v>44015</v>
-      </c>
-      <c r="O15" t="s">
-        <v>3</v>
-      </c>
-      <c r="P15">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="G16" t="s">
-        <v>5</v>
-      </c>
-      <c r="H16" s="2">
-        <v>43740</v>
-      </c>
-      <c r="I16" t="s">
-        <v>3</v>
-      </c>
-      <c r="J16">
-        <v>10</v>
-      </c>
-      <c r="M16" t="s">
-        <v>2</v>
-      </c>
-      <c r="N16" s="2">
-        <v>44025</v>
-      </c>
-      <c r="O16">
-        <v>15</v>
-      </c>
-      <c r="P16" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="17" spans="8:16" x14ac:dyDescent="0.35">
-      <c r="H17" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="I17">
-        <v>155</v>
-      </c>
-      <c r="J17">
-        <v>85</v>
-      </c>
-      <c r="M17" t="s">
-        <v>2</v>
-      </c>
-      <c r="N17" s="2">
-        <v>44026</v>
-      </c>
-      <c r="O17">
-        <v>15</v>
-      </c>
-      <c r="P17" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18" spans="8:16" x14ac:dyDescent="0.35">
-      <c r="M18" t="s">
-        <v>2</v>
-      </c>
-      <c r="N18" s="2">
-        <v>44032</v>
-      </c>
-      <c r="O18">
-        <v>30</v>
-      </c>
-      <c r="P18" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="19" spans="8:16" x14ac:dyDescent="0.35">
-      <c r="N19" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="O19">
-        <v>140</v>
-      </c>
-      <c r="P19">
-        <v>120</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6921E1DB-064A-460D-8545-1BBFD5A246C3}">
   <dimension ref="A1:E48"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -967,13 +414,13 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D1" t="s">
         <v>0</v>
@@ -987,9 +434,9 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C2" s="2">
+        <v>4</v>
+      </c>
+      <c r="C2" s="1">
         <v>43560</v>
       </c>
     </row>
@@ -998,9 +445,9 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C3" s="2">
+        <v>4</v>
+      </c>
+      <c r="C3" s="1">
         <v>43584</v>
       </c>
       <c r="D3">
@@ -1012,9 +459,9 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C4" s="2">
+        <v>4</v>
+      </c>
+      <c r="C4" s="1">
         <v>43585</v>
       </c>
       <c r="D4">
@@ -1026,9 +473,9 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C5" s="2">
+        <v>4</v>
+      </c>
+      <c r="C5" s="1">
         <v>43588</v>
       </c>
       <c r="D5">
@@ -1040,9 +487,9 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C6" s="2">
+        <v>4</v>
+      </c>
+      <c r="C6" s="1">
         <v>43591</v>
       </c>
       <c r="D6">
@@ -1054,9 +501,9 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C7" s="2">
+        <v>4</v>
+      </c>
+      <c r="C7" s="1">
         <v>43595</v>
       </c>
       <c r="D7">
@@ -1068,9 +515,9 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>6</v>
-      </c>
-      <c r="C8" s="2">
+        <v>4</v>
+      </c>
+      <c r="C8" s="1">
         <v>43606</v>
       </c>
       <c r="D8">
@@ -1082,9 +529,9 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>6</v>
-      </c>
-      <c r="C9" s="2">
+        <v>4</v>
+      </c>
+      <c r="C9" s="1">
         <v>43612</v>
       </c>
       <c r="E9">
@@ -1096,9 +543,9 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>6</v>
-      </c>
-      <c r="C10" s="2">
+        <v>4</v>
+      </c>
+      <c r="C10" s="1">
         <v>43616</v>
       </c>
       <c r="E10">
@@ -1110,9 +557,9 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>6</v>
-      </c>
-      <c r="C11" s="2">
+        <v>4</v>
+      </c>
+      <c r="C11" s="1">
         <v>43621</v>
       </c>
       <c r="E11">
@@ -1124,9 +571,9 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>6</v>
-      </c>
-      <c r="C12" s="2">
+        <v>4</v>
+      </c>
+      <c r="C12" s="1">
         <v>43628</v>
       </c>
     </row>
@@ -1135,9 +582,9 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>5</v>
-      </c>
-      <c r="C13" s="2">
+        <v>3</v>
+      </c>
+      <c r="C13" s="1">
         <v>43651</v>
       </c>
     </row>
@@ -1146,9 +593,9 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>5</v>
-      </c>
-      <c r="C14" s="2">
+        <v>3</v>
+      </c>
+      <c r="C14" s="1">
         <v>43651</v>
       </c>
       <c r="D14">
@@ -1160,9 +607,9 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>5</v>
-      </c>
-      <c r="C15" s="2">
+        <v>3</v>
+      </c>
+      <c r="C15" s="1">
         <v>43658</v>
       </c>
       <c r="D15">
@@ -1174,9 +621,9 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>5</v>
-      </c>
-      <c r="C16" s="2">
+        <v>3</v>
+      </c>
+      <c r="C16" s="1">
         <v>43663</v>
       </c>
       <c r="D16">
@@ -1188,9 +635,9 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>5</v>
-      </c>
-      <c r="C17" s="2">
+        <v>3</v>
+      </c>
+      <c r="C17" s="1">
         <v>43670</v>
       </c>
       <c r="D17">
@@ -1202,9 +649,9 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>5</v>
-      </c>
-      <c r="C18" s="2">
+        <v>3</v>
+      </c>
+      <c r="C18" s="1">
         <v>43675</v>
       </c>
       <c r="D18">
@@ -1216,9 +663,9 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>5</v>
-      </c>
-      <c r="C19" s="2">
+        <v>3</v>
+      </c>
+      <c r="C19" s="1">
         <v>43680</v>
       </c>
       <c r="D19">
@@ -1230,9 +677,9 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>5</v>
-      </c>
-      <c r="C20" s="2">
+        <v>3</v>
+      </c>
+      <c r="C20" s="1">
         <v>43685</v>
       </c>
       <c r="D20">
@@ -1244,9 +691,9 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>5</v>
-      </c>
-      <c r="C21" s="2">
+        <v>3</v>
+      </c>
+      <c r="C21" s="1">
         <v>43693</v>
       </c>
       <c r="D21">
@@ -1258,9 +705,9 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>5</v>
-      </c>
-      <c r="C22" s="2">
+        <v>3</v>
+      </c>
+      <c r="C22" s="1">
         <v>43701</v>
       </c>
       <c r="E22">
@@ -1272,9 +719,9 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>5</v>
-      </c>
-      <c r="C23" s="2">
+        <v>3</v>
+      </c>
+      <c r="C23" s="1">
         <v>43707</v>
       </c>
       <c r="D23">
@@ -1286,9 +733,9 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>5</v>
-      </c>
-      <c r="C24" s="2">
+        <v>3</v>
+      </c>
+      <c r="C24" s="1">
         <v>43714</v>
       </c>
       <c r="E24">
@@ -1300,9 +747,9 @@
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>5</v>
-      </c>
-      <c r="C25" s="2">
+        <v>3</v>
+      </c>
+      <c r="C25" s="1">
         <v>43721</v>
       </c>
       <c r="D25">
@@ -1314,9 +761,9 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>5</v>
-      </c>
-      <c r="C26" s="2">
+        <v>3</v>
+      </c>
+      <c r="C26" s="1">
         <v>43728</v>
       </c>
       <c r="E26">
@@ -1328,9 +775,9 @@
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>5</v>
-      </c>
-      <c r="C27" s="2">
+        <v>3</v>
+      </c>
+      <c r="C27" s="1">
         <v>43735</v>
       </c>
       <c r="E27">
@@ -1342,9 +789,9 @@
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>5</v>
-      </c>
-      <c r="C28" s="2">
+        <v>3</v>
+      </c>
+      <c r="C28" s="1">
         <v>43740</v>
       </c>
       <c r="E28">
@@ -1356,9 +803,9 @@
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>5</v>
-      </c>
-      <c r="C29" s="2">
+        <v>3</v>
+      </c>
+      <c r="C29" s="1">
         <v>43755</v>
       </c>
     </row>
@@ -1369,7 +816,7 @@
       <c r="B30" t="s">
         <v>2</v>
       </c>
-      <c r="C30" s="2">
+      <c r="C30" s="1">
         <v>43938</v>
       </c>
       <c r="D30">
@@ -1383,7 +830,7 @@
       <c r="B31" t="s">
         <v>2</v>
       </c>
-      <c r="C31" s="2">
+      <c r="C31" s="1">
         <v>43940</v>
       </c>
     </row>
@@ -1394,7 +841,7 @@
       <c r="B32" t="s">
         <v>2</v>
       </c>
-      <c r="C32" s="2">
+      <c r="C32" s="1">
         <v>43941</v>
       </c>
       <c r="D32">
@@ -1408,7 +855,7 @@
       <c r="B33" t="s">
         <v>2</v>
       </c>
-      <c r="C33" s="2">
+      <c r="C33" s="1">
         <v>43957</v>
       </c>
       <c r="D33">
@@ -1422,7 +869,7 @@
       <c r="B34" t="s">
         <v>2</v>
       </c>
-      <c r="C34" s="2">
+      <c r="C34" s="1">
         <v>43971</v>
       </c>
       <c r="D34">
@@ -1436,7 +883,7 @@
       <c r="B35" t="s">
         <v>2</v>
       </c>
-      <c r="C35" s="2">
+      <c r="C35" s="1">
         <v>43976</v>
       </c>
       <c r="E35">
@@ -1450,7 +897,7 @@
       <c r="B36" t="s">
         <v>2</v>
       </c>
-      <c r="C36" s="2">
+      <c r="C36" s="1">
         <v>43977</v>
       </c>
       <c r="E36">
@@ -1464,7 +911,7 @@
       <c r="B37" t="s">
         <v>2</v>
       </c>
-      <c r="C37" s="2">
+      <c r="C37" s="1">
         <v>43986</v>
       </c>
       <c r="D37">
@@ -1478,7 +925,7 @@
       <c r="B38" t="s">
         <v>2</v>
       </c>
-      <c r="C38" s="2">
+      <c r="C38" s="1">
         <v>43993</v>
       </c>
       <c r="E38">
@@ -1492,7 +939,7 @@
       <c r="B39" t="s">
         <v>2</v>
       </c>
-      <c r="C39" s="2">
+      <c r="C39" s="1">
         <v>43994</v>
       </c>
       <c r="E39">
@@ -1506,7 +953,7 @@
       <c r="B40" t="s">
         <v>2</v>
       </c>
-      <c r="C40" s="2">
+      <c r="C40" s="1">
         <v>43999</v>
       </c>
       <c r="D40">
@@ -1520,7 +967,7 @@
       <c r="B41" t="s">
         <v>2</v>
       </c>
-      <c r="C41" s="2">
+      <c r="C41" s="1">
         <v>44005</v>
       </c>
       <c r="E41">
@@ -1534,7 +981,7 @@
       <c r="B42" t="s">
         <v>2</v>
       </c>
-      <c r="C42" s="2">
+      <c r="C42" s="1">
         <v>44006</v>
       </c>
       <c r="E42">
@@ -1548,7 +995,7 @@
       <c r="B43" t="s">
         <v>2</v>
       </c>
-      <c r="C43" s="2">
+      <c r="C43" s="1">
         <v>44014</v>
       </c>
       <c r="E43">
@@ -1562,7 +1009,7 @@
       <c r="B44" t="s">
         <v>2</v>
       </c>
-      <c r="C44" s="2">
+      <c r="C44" s="1">
         <v>44015</v>
       </c>
       <c r="E44">
@@ -1576,7 +1023,7 @@
       <c r="B45" t="s">
         <v>2</v>
       </c>
-      <c r="C45" s="2">
+      <c r="C45" s="1">
         <v>44025</v>
       </c>
       <c r="D45">
@@ -1590,7 +1037,7 @@
       <c r="B46" t="s">
         <v>2</v>
       </c>
-      <c r="C46" s="2">
+      <c r="C46" s="1">
         <v>44026</v>
       </c>
       <c r="D46">
@@ -1604,7 +1051,7 @@
       <c r="B47" t="s">
         <v>2</v>
       </c>
-      <c r="C47" s="2">
+      <c r="C47" s="1">
         <v>44032</v>
       </c>
       <c r="D47">
@@ -1618,7 +1065,7 @@
       <c r="B48" t="s">
         <v>2</v>
       </c>
-      <c r="C48" s="2">
+      <c r="C48" s="1">
         <v>44047</v>
       </c>
     </row>
